--- a/data/raw/1-200-lijst-in-excel.xlsx
+++ b/data/raw/1-200-lijst-in-excel.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woudsmar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE2928F-E295-408A-B5D1-30BCA25B1842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA3755E1-4EED-4108-9F91-FC102844E5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3A059B61-36D2-49E7-8843-88B4A6B437F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1-200-lijst-in-excel" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="148">
   <si>
     <t>Benaming</t>
   </si>
@@ -305,12 +305,6 @@
     <t>Trompstraat 1</t>
   </si>
   <si>
-    <t>Totaal</t>
-  </si>
-  <si>
-    <t>waarvan 390 afgerond/gestart</t>
-  </si>
-  <si>
     <t>Optopping</t>
   </si>
   <si>
@@ -434,9 +428,6 @@
     <t>Kalmoes</t>
   </si>
   <si>
-    <t>Nabij Nautisch Kwartier</t>
-  </si>
-  <si>
     <t>Buurtwinkelcentrum</t>
   </si>
   <si>
@@ -486,13 +477,19 @@
   </si>
   <si>
     <t>Inpassen angrenzend aan bestaand winkelcentrum</t>
+  </si>
+  <si>
+    <t>Mastspoor 1, Huizen</t>
+  </si>
+  <si>
+    <t>Kostmand 2-18, Huizen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -509,13 +506,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -579,22 +569,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -931,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26706CBE-0DD1-4C88-8532-447103C482C4}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.33203125" customWidth="1"/>
@@ -957,7 +941,7 @@
         <v>42</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
@@ -968,10 +952,10 @@
     </row>
     <row r="2" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4">
         <v>6</v>
@@ -987,7 +971,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>4</v>
@@ -1049,10 +1033,10 @@
         <v>34</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>48</v>
@@ -1070,10 +1054,10 @@
         <v>52</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>13</v>
@@ -1091,10 +1075,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
@@ -1112,10 +1096,10 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>17</v>
@@ -1133,10 +1117,10 @@
         <v>52</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>6</v>
@@ -1154,10 +1138,10 @@
         <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
@@ -1197,7 +1181,7 @@
         <v>50</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>6</v>
@@ -1218,7 +1202,7 @@
         <v>50</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>6</v>
@@ -1293,10 +1277,10 @@
         <v>6</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
@@ -1336,7 +1320,7 @@
         <v>53</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>6</v>
@@ -1357,7 +1341,7 @@
         <v>54</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>6</v>
@@ -1378,7 +1362,7 @@
         <v>56</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>35</v>
@@ -1399,7 +1383,7 @@
         <v>56</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
@@ -1496,7 +1480,7 @@
         <v>53</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>6</v>
@@ -1514,10 +1498,10 @@
         <v>4</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>35</v>
@@ -1557,7 +1541,7 @@
         <v>5</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>72</v>
@@ -1566,57 +1550,57 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C32" s="4">
         <v>3</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
     </row>
     <row r="33" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C33" s="4">
         <v>15</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
     </row>
     <row r="34" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C34" s="4">
         <v>8</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -1635,7 +1619,7 @@
         <v>75</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>76</v>
@@ -1658,7 +1642,7 @@
         <v>79</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>6</v>
@@ -1679,7 +1663,7 @@
         <v>82</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>10</v>
@@ -1719,7 +1703,7 @@
         <v>40</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F39" s="4"/>
       <c r="G39" s="4" t="s">
@@ -1728,54 +1712,54 @@
     </row>
     <row r="40" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C40" s="4">
         <v>2</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C41" s="4">
         <v>15</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C42" s="4">
         <v>3</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -1783,138 +1767,125 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C43" s="4">
         <v>3</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="6">
-        <f>SUM(C2:C43)</f>
-        <v>1253</v>
-      </c>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="F46" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C47" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C48" t="s">
+        <v>130</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" t="s">
+        <v>130</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C49" t="s">
-        <v>133</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C50" t="s">
-        <v>133</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>
